--- a/data/trans_camb/IMC_inf_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_R2-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 19,85</t>
+          <t>-1,48; 19,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 19,98</t>
+          <t>-2,6; 19,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 7,42</t>
+          <t>-11,49; 8,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 12,91</t>
+          <t>-8,66; 12,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 13,94</t>
+          <t>-6,75; 13,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,14; 4,35</t>
+          <t>-23,88; 2,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 13,16</t>
+          <t>-2,87; 13,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 13,7</t>
+          <t>-1,9; 13,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 2,78</t>
+          <t>-14,6; 2,91</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 70,65</t>
+          <t>-3,96; 69,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 69,84</t>
+          <t>-6,64; 66,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,43; 26,31</t>
+          <t>-30,76; 35,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 30,14</t>
+          <t>-17,34; 30,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 33,27</t>
+          <t>-13,76; 30,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,04; 8,83</t>
+          <t>-46,44; 4,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 36,14</t>
+          <t>-6,46; 35,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 36,7</t>
+          <t>-4,23; 37,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-32,77; 7,34</t>
+          <t>-33,33; 7,82</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 11,32</t>
+          <t>-5,44; 12,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,79; -1,29</t>
+          <t>-17,38; -1,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,99; -0,9</t>
+          <t>-17,68; -1,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 15,39</t>
+          <t>-0,63; 15,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 5,27</t>
+          <t>-11,24; 5,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 1,35</t>
+          <t>-16,51; 1,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 11,23</t>
+          <t>-0,57; 11,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,81; -0,33</t>
+          <t>-11,87; 0,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-13,69; -0,83</t>
+          <t>-14,6; -1,78</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 35,31</t>
+          <t>-13,24; 35,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-41,31; -4,58</t>
+          <t>-42,09; -4,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,35; -3,43</t>
+          <t>-42,91; -3,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 35,22</t>
+          <t>-1,18; 35,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,57; 12,19</t>
+          <t>-21,84; 12,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,61; 3,21</t>
+          <t>-31,75; 3,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 28,0</t>
+          <t>-1,25; 28,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,72; -0,77</t>
+          <t>-25,43; 1,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-30,34; -2,05</t>
+          <t>-31,42; -4,69</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 18,32</t>
+          <t>-2,64; 16,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 10,04</t>
+          <t>-8,76; 10,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 5,19</t>
+          <t>-19,26; 5,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 12,38</t>
+          <t>-7,75; 11,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 4,64</t>
+          <t>-15,8; 3,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 5,61</t>
+          <t>-16,04; 5,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 11,46</t>
+          <t>-2,64; 11,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 4,37</t>
+          <t>-9,3; 3,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-16,23; 1,69</t>
+          <t>-15,39; 1,31</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 66,23</t>
+          <t>-5,85; 59,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,87; 34,32</t>
+          <t>-22,64; 37,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-55,08; 18,02</t>
+          <t>-50,47; 16,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 31,67</t>
+          <t>-15,35; 29,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,15; 11,76</t>
+          <t>-32,85; 8,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-34,74; 13,77</t>
+          <t>-33,15; 12,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 31,93</t>
+          <t>-6,53; 32,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-22,13; 12,36</t>
+          <t>-21,61; 10,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-38,6; 3,97</t>
+          <t>-37,6; 3,34</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 17,99</t>
+          <t>-0,98; 17,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 11,28</t>
+          <t>-7,12; 10,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 1,57</t>
+          <t>-16,33; 2,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 16,49</t>
+          <t>-1,73; 16,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 13,6</t>
+          <t>-5,27; 13,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 4,96</t>
+          <t>-13,67; 4,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 14,54</t>
+          <t>1,25; 14,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 10,15</t>
+          <t>-2,28; 9,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 1,56</t>
+          <t>-12,18; 1,26</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 56,98</t>
+          <t>-2,57; 55,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,47; 36,4</t>
+          <t>-17,55; 35,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,86; 6,96</t>
+          <t>-40,83; 8,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 45,09</t>
+          <t>-3,86; 44,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 36,28</t>
+          <t>-11,65; 37,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-29,78; 12,96</t>
+          <t>-30,09; 14,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,98; 41,59</t>
+          <t>3,38; 40,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 28,25</t>
+          <t>-5,74; 27,33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-28,59; 4,29</t>
+          <t>-30,29; 2,88</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,48; 11,51</t>
+          <t>2,04; 11,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 4,31</t>
+          <t>-5,07; 4,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,89; -1,84</t>
+          <t>-12,44; -1,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 10,03</t>
+          <t>0,19; 9,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 4,46</t>
+          <t>-5,29; 4,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,87; -1,14</t>
+          <t>-11,59; -1,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,21; 9,16</t>
+          <t>2,4; 9,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 2,5</t>
+          <t>-3,72; 3,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-10,41; -2,69</t>
+          <t>-10,27; -2,84</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>6,62; 35,38</t>
+          <t>5,64; 35,67</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 13,13</t>
+          <t>-13,37; 12,2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-34,68; -5,62</t>
+          <t>-33,62; -5,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,06; 22,95</t>
+          <t>0,52; 22,72</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 10,07</t>
+          <t>-11,35; 9,58</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-25,02; -2,62</t>
+          <t>-24,39; -2,83</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,25; 23,49</t>
+          <t>5,61; 23,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 6,44</t>
+          <t>-8,93; 7,99</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-25,15; -7,02</t>
+          <t>-24,7; -7,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_R2-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado</t>
+          <t>Población con sobrepeso u obesidad declarado por los/as progenitores/as</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 19,74</t>
+          <t>-0,83; 20,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 19,43</t>
+          <t>-3,24; 19,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 8,64</t>
+          <t>-12,09; 7,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 12,7</t>
+          <t>-8,46; 12,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 13,28</t>
+          <t>-7,43; 14,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,88; 2,08</t>
+          <t>-21,66; 4,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 13,24</t>
+          <t>-2,96; 13,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 13,89</t>
+          <t>-1,73; 13,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 2,91</t>
+          <t>-14,28; 2,36</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 69,45</t>
+          <t>-2,67; 73,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 66,0</t>
+          <t>-7,59; 69,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-30,76; 35,25</t>
+          <t>-32,19; 28,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 30,36</t>
+          <t>-16,3; 30,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 30,9</t>
+          <t>-14,0; 34,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,44; 4,56</t>
+          <t>-43,5; 10,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 35,84</t>
+          <t>-6,54; 35,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 37,33</t>
+          <t>-3,87; 36,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-33,33; 7,82</t>
+          <t>-32,58; 6,35</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 12,15</t>
+          <t>-6,33; 11,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,38; -1,52</t>
+          <t>-17,96; -1,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,68; -1,02</t>
+          <t>-17,31; -1,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 15,69</t>
+          <t>-1,59; 15,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 5,4</t>
+          <t>-11,99; 5,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 1,87</t>
+          <t>-15,7; 2,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 11,46</t>
+          <t>-0,66; 11,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,87; 0,4</t>
+          <t>-11,96; -0,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,6; -1,78</t>
+          <t>-14,3; -1,81</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 35,92</t>
+          <t>-14,06; 34,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-42,09; -4,18</t>
+          <t>-42,16; -5,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,91; -3,01</t>
+          <t>-43,13; -4,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 35,32</t>
+          <t>-3,05; 34,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,84; 12,27</t>
+          <t>-23,02; 11,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,75; 3,86</t>
+          <t>-29,78; 5,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 28,59</t>
+          <t>-1,48; 27,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,43; 1,03</t>
+          <t>-25,8; -0,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-31,42; -4,69</t>
+          <t>-30,64; -4,52</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 16,78</t>
+          <t>-3,52; 16,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 10,25</t>
+          <t>-9,06; 10,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,26; 5,4</t>
+          <t>-20,76; 4,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 11,65</t>
+          <t>-7,47; 12,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 3,44</t>
+          <t>-16,44; 3,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 5,16</t>
+          <t>-16,77; 4,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 11,74</t>
+          <t>-1,49; 13,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 3,68</t>
+          <t>-10,11; 4,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-15,39; 1,31</t>
+          <t>-15,23; 1,92</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 59,26</t>
+          <t>-9,36; 58,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,64; 37,99</t>
+          <t>-23,72; 36,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-50,47; 16,61</t>
+          <t>-55,93; 13,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 29,29</t>
+          <t>-15,34; 31,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,85; 8,18</t>
+          <t>-32,49; 8,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,15; 12,34</t>
+          <t>-33,75; 12,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 32,55</t>
+          <t>-3,56; 38,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-21,61; 10,73</t>
+          <t>-23,52; 12,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-37,6; 3,34</t>
+          <t>-36,26; 5,05</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 17,31</t>
+          <t>0,55; 17,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 10,96</t>
+          <t>-7,35; 10,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,33; 2,57</t>
+          <t>-15,65; 2,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 16,17</t>
+          <t>-2,84; 15,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 13,41</t>
+          <t>-4,59; 13,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 4,77</t>
+          <t>-13,31; 5,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 14,44</t>
+          <t>1,95; 15,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 9,51</t>
+          <t>-2,41; 10,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 1,26</t>
+          <t>-11,49; 1,39</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 55,1</t>
+          <t>1,27; 56,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,55; 35,01</t>
+          <t>-18,49; 33,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-40,83; 8,44</t>
+          <t>-40,29; 6,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 44,19</t>
+          <t>-6,52; 42,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 37,24</t>
+          <t>-10,32; 37,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,09; 14,03</t>
+          <t>-29,25; 15,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,38; 40,58</t>
+          <t>4,78; 43,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 27,33</t>
+          <t>-6,16; 29,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-30,29; 2,88</t>
+          <t>-28,03; 3,83</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,04; 11,6</t>
+          <t>1,83; 11,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 4,02</t>
+          <t>-5,25; 4,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,44; -1,78</t>
+          <t>-12,63; -2,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 9,63</t>
+          <t>0,55; 9,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 4,11</t>
+          <t>-5,36; 3,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,59; -1,2</t>
+          <t>-11,85; -1,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,4; 9,1</t>
+          <t>2,56; 9,3</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 3,11</t>
+          <t>-3,83; 2,57</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-10,27; -2,84</t>
+          <t>-10,42; -2,97</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5,64; 35,67</t>
+          <t>4,78; 34,78</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 12,2</t>
+          <t>-14,07; 12,54</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-33,62; -5,68</t>
+          <t>-33,49; -5,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,52; 22,72</t>
+          <t>1,27; 23,1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 9,58</t>
+          <t>-11,06; 8,93</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-24,39; -2,83</t>
+          <t>-24,43; -3,51</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,61; 23,41</t>
+          <t>6,45; 24,29</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 7,99</t>
+          <t>-9,11; 6,6</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-24,7; -7,04</t>
+          <t>-24,83; -7,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_R2-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,05</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-6,95</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>9,03</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>8,87</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,78</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,38</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,05</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-9,18</t>
+          <t>-3,56</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-5,98</t>
+          <t>-5,45</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 20,14</t>
+          <t>-8,75; 12,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 19,38</t>
+          <t>-7,25; 13,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 7,82</t>
+          <t>-19,5; 6,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 12,8</t>
+          <t>-2,17; 19,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 14,9</t>
+          <t>-2,65; 19,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,66; 4,58</t>
+          <t>-13,92; 6,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 13,02</t>
+          <t>-1,93; 13,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 13,49</t>
+          <t>-1,76; 13,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,28; 2,36</t>
+          <t>-13,28; 2,74</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,06%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6,48%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-14,76%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>27,17%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>26,68%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-8,37%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,48%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-19,49%</t>
+          <t>-10,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-14,74%</t>
+          <t>-13,42%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 73,75</t>
+          <t>-16,6; 30,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 69,72</t>
+          <t>-14,16; 33,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-32,19; 28,72</t>
+          <t>-38,59; 13,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,3; 30,23</t>
+          <t>-5,51; 70,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 34,33</t>
+          <t>-6,92; 69,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,5; 10,77</t>
+          <t>-36,88; 22,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 35,19</t>
+          <t>-4,13; 36,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 36,93</t>
+          <t>-4,02; 36,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-32,58; 6,35</t>
+          <t>-31,2; 6,9</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,15</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-3,42</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-7,27</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,23</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-9,17</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-9,61</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,15</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-3,42</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-7,49</t>
+          <t>-9,39</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-7,9</t>
+          <t>-7,79</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 11,5</t>
+          <t>-2,11; 15,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,96; -1,74</t>
+          <t>-11,53; 5,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,31; -1,26</t>
+          <t>-15,91; 1,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 15,46</t>
+          <t>-5,14; 11,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 5,0</t>
+          <t>-16,79; -1,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 2,25</t>
+          <t>-17,57; -0,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 11,06</t>
+          <t>-0,93; 11,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,96; -0,16</t>
+          <t>-11,81; -0,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,3; -1,81</t>
+          <t>-13,52; -0,8</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14,74%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-7,04%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-14,97%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>8,56%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-24,32%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-25,48%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14,74%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-7,04%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-15,43%</t>
+          <t>-24,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-18,24%</t>
+          <t>-18,0%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,06; 34,4</t>
+          <t>-3,27; 35,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-42,16; -5,03</t>
+          <t>-22,57; 12,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,13; -4,5</t>
+          <t>-30,02; 2,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 34,35</t>
+          <t>-12,21; 35,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 11,1</t>
+          <t>-41,31; -4,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,78; 5,29</t>
+          <t>-42,83; -3,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 27,17</t>
+          <t>-2,05; 28,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,8; -0,39</t>
+          <t>-25,72; -0,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-30,64; -4,52</t>
+          <t>-29,89; -1,93</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,23</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-6,29</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-5,85</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>7,63</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,61</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-6,03</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,23</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-6,29</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-6,09</t>
+          <t>-3,15</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-6,28</t>
+          <t>-4,44</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 16,88</t>
+          <t>-7,93; 12,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 10,27</t>
+          <t>-15,68; 4,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,76; 4,36</t>
+          <t>-16,8; 6,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 12,69</t>
+          <t>-1,42; 18,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,44; 3,45</t>
+          <t>-8,63; 10,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 4,77</t>
+          <t>-12,06; 6,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 13,24</t>
+          <t>-2,18; 11,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 4,47</t>
+          <t>-9,43; 4,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-15,23; 1,92</t>
+          <t>-11,53; 2,55</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-13,98%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-12,99%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>22,87%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1,83%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-18,07%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-13,98%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-13,53%</t>
+          <t>-9,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-15,97%</t>
+          <t>-11,28%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 58,88</t>
+          <t>-16,46; 31,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,72; 36,84</t>
+          <t>-32,15; 11,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-55,93; 13,82</t>
+          <t>-34,49; 14,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 31,6</t>
+          <t>-3,93; 66,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,49; 8,51</t>
+          <t>-22,87; 34,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,75; 12,41</t>
+          <t>-32,43; 21,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 38,46</t>
+          <t>-5,11; 31,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,52; 12,81</t>
+          <t>-22,13; 12,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-36,26; 5,05</t>
+          <t>-27,25; 6,94</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7,07</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4,6</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-4,83</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>8,8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2,08</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-7,09</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7,07</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,6</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,08</t>
+          <t>-9,0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-5,43</t>
+          <t>-6,91</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 17,33</t>
+          <t>-1,82; 16,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 10,22</t>
+          <t>-4,42; 13,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 2,29</t>
+          <t>-13,88; 3,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 15,64</t>
+          <t>-0,51; 17,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 13,62</t>
+          <t>-7,41; 11,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 5,09</t>
+          <t>-18,82; -0,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 15,09</t>
+          <t>1,25; 14,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 10,28</t>
+          <t>-2,65; 10,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 1,39</t>
+          <t>-13,1; -0,58</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>17,21%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11,19%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-11,76%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>24,85%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>5,88%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-20,03%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>17,21%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>11,19%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-9,92%</t>
+          <t>-25,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-14,22%</t>
+          <t>-18,08%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,27; 56,3</t>
+          <t>-4,42; 45,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,49; 33,37</t>
+          <t>-9,65; 36,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-40,29; 6,97</t>
+          <t>-31,55; 10,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 42,79</t>
+          <t>-1,66; 56,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 37,79</t>
+          <t>-19,47; 36,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-29,25; 15,39</t>
+          <t>-46,48; -0,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,78; 43,89</t>
+          <t>2,98; 41,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 29,93</t>
+          <t>-6,43; 28,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-28,03; 3,83</t>
+          <t>-32,06; -1,74</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5,06</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,69</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-6,05</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>6,91</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-0,37</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-6,91</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5,06</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-6,42</t>
+          <t>-6,7</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-6,45</t>
+          <t>-6,2</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,83; 11,66</t>
+          <t>0,19; 10,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 4,14</t>
+          <t>-5,13; 4,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,63; -2,38</t>
+          <t>-11,69; -1,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,55; 9,92</t>
+          <t>2,48; 11,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 3,84</t>
+          <t>-4,92; 4,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,85; -1,55</t>
+          <t>-11,13; -2,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,56; 9,3</t>
+          <t>2,21; 9,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 2,57</t>
+          <t>-3,78; 2,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-10,42; -2,97</t>
+          <t>-9,67; -2,94</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>11,15%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-1,52%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-13,31%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>19,61%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-1,04%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-19,61%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-1,52%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-14,14%</t>
+          <t>-19,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-15,94%</t>
+          <t>-15,32%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>4,78; 34,78</t>
+          <t>0,06; 22,95</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-14,07; 12,54</t>
+          <t>-10,85; 10,07</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-33,49; -5,96</t>
+          <t>-24,75; -2,61</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,27; 23,1</t>
+          <t>6,62; 35,38</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 8,93</t>
+          <t>-13,21; 13,13</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-24,43; -3,51</t>
+          <t>-29,92; -6,45</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,45; 24,29</t>
+          <t>5,25; 23,49</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 6,6</t>
+          <t>-9,02; 6,44</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-24,83; -7,7</t>
+          <t>-23,14; -7,25</t>
         </is>
       </c>
     </row>
